--- a/data/IIP_VNM.xlsx
+++ b/data/IIP_VNM.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="159">
   <si>
     <t>DATASTRUCTURE</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
   </si>
   <si>
     <t>AIP_ISIC4_IX</t>
@@ -786,10 +789,9 @@
       <sheetName val="Cac thang chinh thuc 2026"/>
       <sheetName val="Ty le dong gop"/>
       <sheetName val="Cac thang so cung ky"/>
-      <sheetName val="IIP 6 thang cac nam"/>
+      <sheetName val="IIP 7 thang cac nam"/>
       <sheetName val="Chi so so nam goc"/>
       <sheetName val="Lao dong"/>
-      <sheetName val="San pham"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -810,7 +812,10 @@
             <v>204.45</v>
           </cell>
           <cell r="H6">
-            <v>211.66</v>
+            <v>212.09</v>
+          </cell>
+          <cell r="I6">
+            <v>214.6</v>
           </cell>
         </row>
         <row r="7">
@@ -830,7 +835,10 @@
             <v>75.27</v>
           </cell>
           <cell r="H7">
-            <v>75.53</v>
+            <v>76.66</v>
+          </cell>
+          <cell r="I7">
+            <v>75.069999999999993</v>
           </cell>
         </row>
         <row r="13">
@@ -850,7 +858,10 @@
             <v>226.74</v>
           </cell>
           <cell r="H13">
-            <v>234.91</v>
+            <v>235.5</v>
+          </cell>
+          <cell r="I13">
+            <v>239.83</v>
           </cell>
         </row>
         <row r="38">
@@ -870,7 +881,10 @@
             <v>246.62</v>
           </cell>
           <cell r="H38">
-            <v>258.55</v>
+            <v>255.72</v>
+          </cell>
+          <cell r="I38">
+            <v>251.17</v>
           </cell>
         </row>
         <row r="40">
@@ -890,7 +904,10 @@
             <v>212.57</v>
           </cell>
           <cell r="H40">
-            <v>218.03</v>
+            <v>222.02</v>
+          </cell>
+          <cell r="I40">
+            <v>220.32</v>
           </cell>
         </row>
       </sheetData>
@@ -902,7 +919,6 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1171,10 +1187,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DO26"/>
+  <dimension ref="A1:DP26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1233,7 +1249,7 @@
       <c r="AX1" s="4"/>
       <c r="AY1" s="4"/>
     </row>
-    <row r="2" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1292,7 +1308,7 @@
       <c r="AX2" s="4"/>
       <c r="AY2" s="4"/>
     </row>
-    <row r="3" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1351,7 +1367,7 @@
       <c r="AX3" s="4"/>
       <c r="AY3" s="4"/>
     </row>
-    <row r="4" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -1410,7 +1426,7 @@
       <c r="AX4" s="4"/>
       <c r="AY4" s="4"/>
     </row>
-    <row r="5" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:120" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
@@ -1469,7 +1485,7 @@
       <c r="AX5" s="4"/>
       <c r="AY5" s="4"/>
     </row>
-    <row r="6" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
@@ -1528,7 +1544,7 @@
       <c r="AX6" s="4"/>
       <c r="AY6" s="4"/>
     </row>
-    <row r="7" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1587,7 +1603,7 @@
       <c r="AX7" s="4"/>
       <c r="AY7" s="4"/>
     </row>
-    <row r="8" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:120" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>20</v>
       </c>
@@ -1646,7 +1662,7 @@
       <c r="AX8" s="4"/>
       <c r="AY8" s="4"/>
     </row>
-    <row r="9" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:120" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -1698,11 +1714,11 @@
       <c r="AW9" s="4"/>
       <c r="AX9" s="4"/>
       <c r="AY9" s="4"/>
-      <c r="DO9" t="s">
+      <c r="DP9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:119" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:120" s="21" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>24</v>
       </c>
@@ -2060,19 +2076,22 @@
       <c r="DO10" s="21" t="s">
         <v>142</v>
       </c>
+      <c r="DP10" s="21" t="s">
+        <v>143</v>
+      </c>
     </row>
-    <row r="11" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="22">
         <v>2015</v>
@@ -2417,27 +2436,31 @@
         <f>+'[1]IIP (C2)'!F6</f>
         <v>191.38</v>
       </c>
-      <c r="DN11">
+      <c r="DN11" s="25">
         <f>+'[1]IIP (C2)'!G6</f>
         <v>204.45</v>
       </c>
-      <c r="DO11">
+      <c r="DO11" s="25">
         <f>+'[1]IIP (C2)'!H6</f>
-        <v>211.66</v>
+        <v>212.09</v>
+      </c>
+      <c r="DP11" s="25">
+        <f>+'[1]IIP (C2)'!I6</f>
+        <v>214.6</v>
       </c>
     </row>
-    <row r="12" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E12" s="4">
         <v>2015</v>
@@ -2782,27 +2805,31 @@
         <f>+'[1]IIP (C2)'!F7</f>
         <v>76.489999999999995</v>
       </c>
-      <c r="DN12">
+      <c r="DN12" s="25">
         <f>+'[1]IIP (C2)'!G7</f>
         <v>75.27</v>
       </c>
-      <c r="DO12">
+      <c r="DO12" s="25">
         <f>+'[1]IIP (C2)'!H7</f>
-        <v>75.53</v>
+        <v>76.66</v>
+      </c>
+      <c r="DP12" s="25">
+        <f>+'[1]IIP (C2)'!I7</f>
+        <v>75.069999999999993</v>
       </c>
     </row>
-    <row r="13" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13" s="4">
         <v>2015</v>
@@ -3147,27 +3174,31 @@
         <f>+'[1]IIP (C2)'!F13</f>
         <v>210.43</v>
       </c>
-      <c r="DN13">
+      <c r="DN13" s="25">
         <f>+'[1]IIP (C2)'!G13</f>
         <v>226.74</v>
       </c>
-      <c r="DO13">
+      <c r="DO13" s="25">
         <f>+'[1]IIP (C2)'!H13</f>
-        <v>234.91</v>
+        <v>235.5</v>
+      </c>
+      <c r="DP13" s="25">
+        <f>+'[1]IIP (C2)'!I13</f>
+        <v>239.83</v>
       </c>
     </row>
-    <row r="14" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14" s="4">
         <v>2015</v>
@@ -3512,27 +3543,31 @@
         <f>+'[1]IIP (C2)'!F38</f>
         <v>232.33</v>
       </c>
-      <c r="DN14">
+      <c r="DN14" s="25">
         <f>+'[1]IIP (C2)'!G38</f>
         <v>246.62</v>
       </c>
-      <c r="DO14">
+      <c r="DO14" s="25">
         <f>+'[1]IIP (C2)'!H38</f>
-        <v>258.55</v>
+        <v>255.72</v>
+      </c>
+      <c r="DP14" s="25">
+        <f>+'[1]IIP (C2)'!I38</f>
+        <v>251.17</v>
       </c>
     </row>
-    <row r="15" spans="1:119" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E15" s="4">
         <v>2015</v>
@@ -3877,13 +3912,17 @@
         <f>+'[1]IIP (C2)'!F40</f>
         <v>215.35</v>
       </c>
-      <c r="DN15">
+      <c r="DN15" s="25">
         <f>+'[1]IIP (C2)'!G40</f>
         <v>212.57</v>
       </c>
-      <c r="DO15">
+      <c r="DO15" s="25">
         <f>+'[1]IIP (C2)'!H40</f>
-        <v>218.03</v>
+        <v>222.02</v>
+      </c>
+      <c r="DP15" s="25">
+        <f>+'[1]IIP (C2)'!I40</f>
+        <v>220.32</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
